--- a/databases/tabela_resumo_clusters_sus_final_kmeans3.xlsx
+++ b/databases/tabela_resumo_clusters_sus_final_kmeans3.xlsx
@@ -414,11 +414,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1: lowest unsafe abortion rates</t>
+          <t>1: lowest induced abortion rates</t>
         </is>
       </c>
       <c r="C2">
-        <v>2629</v>
+        <v>2595</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -427,19 +427,19 @@
         <v>1.7</v>
       </c>
       <c r="F2">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="H2">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="I2">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J2">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="3">
@@ -450,26 +450,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2: intermediary unsafe abortion rates</t>
+          <t>2: intermediary induced abortion rates</t>
         </is>
       </c>
       <c r="C3">
-        <v>2249</v>
+        <v>2307</v>
       </c>
       <c r="D3">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="E3">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="F3">
-        <v>7.86</v>
+        <v>7.79</v>
       </c>
       <c r="G3">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="H3">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="I3">
         <v>9.199999999999999</v>
@@ -486,29 +486,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3: highest unsafe abortion rates</t>
+          <t>3: highest induced abortion rates</t>
         </is>
       </c>
       <c r="C4">
-        <v>692</v>
+        <v>668</v>
       </c>
       <c r="D4">
         <v>11.6</v>
       </c>
       <c r="E4">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="F4">
-        <v>15.33</v>
+        <v>15.38</v>
       </c>
       <c r="G4">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="H4">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="I4">
-        <v>16.72</v>
+        <v>16.8</v>
       </c>
       <c r="J4">
         <v>42.7</v>
